--- a/jpcore-r4b/develop/StructureDefinition-jp-practitioner.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-practitioner.xlsx
@@ -69,7 +69,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) (http://jpfhir.jp, office@hlfhir.jp)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -1326,7 +1326,7 @@
   </si>
   <si>
     <t>使用のコンテキストは、範囲全体が適用されるか（例：「患者はこの時間範囲で病院の入院患者であった」）、範囲内の1つの値が適用されるか（例：「この2つの時間の間に患者に与える」）を指定する。  
-期間は、期間(経過時間の尺度)には使用されない。[Duration](http://hl7.org/fhir/R4/datatypes.html#Duration)を参照のこと。</t>
+期間は、期間(経過時間の尺度)には使用されない。[Duration](http://hl7.org/fhir/R4B/datatypes.html#Duration)を参照のこと。</t>
   </si>
   <si>
     <t>資格は期間限定のものが多く、取り消されることもある。</t>

--- a/jpcore-r4b/develop/StructureDefinition-jp-practitioner.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-practitioner.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2851" uniqueCount="525">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2859" uniqueCount="518">
   <si>
     <t>Property</t>
   </si>
@@ -552,7 +552,7 @@
 </t>
   </si>
   <si>
-    <t>人の名前情報、その一部分と使い方</t>
+    <t>The name(s) associated with the practitioner</t>
   </si>
   <si>
     <t>医療従事者の氏名（複数の場合もある）</t>
@@ -572,21 +572,13 @@
     <t>医療従事者が知られている名前。複数ある場合は、従事者が通常知られている名前を表示に使用する。</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
-</t>
-  </si>
-  <si>
-    <t>XPN</t>
-  </si>
-  <si>
-    <t>EN (actually, PN)</t>
-  </si>
-  <si>
-    <t>ProviderName</t>
+    <t>XCN Components</t>
+  </si>
+  <si>
+    <t>./name</t>
+  </si>
+  <si>
+    <t>./PreferredName (GivenNames, FamilyName, TitleCode)</t>
   </si>
   <si>
     <t>Practitioner.telecom</t>
@@ -1233,6 +1225,10 @@
 </t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
+</t>
+  </si>
+  <si>
     <t>CER?</t>
   </si>
   <si>
@@ -1385,12 +1381,6 @@
   </si>
   <si>
     <t>都道府県別 麻薬施用者免許番号</t>
-  </si>
-  <si>
-    <t>An identifier that applies to this person's qualification in this role.</t>
-  </si>
-  <si>
-    <t>Often, specific identities are assigned for the qualification.</t>
   </si>
   <si>
     <t>Practitioner.qualification:narcoticPrescriptionLicenseNumber.identifier.id</t>
@@ -1625,9 +1615,6 @@
     <t>Practitioner.qualification:narcoticPrescriptionLicenseNumber.code</t>
   </si>
   <si>
-    <t>Coded representation of the qualification.</t>
-  </si>
-  <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
     &lt;system value="http://jpfhir.jp/fhir/core/CodeSystem/JP_MedicalLicenseCertificate_CS"/&gt;
@@ -1642,16 +1629,7 @@
     <t>Practitioner.qualification:narcoticPrescriptionLicenseNumber.period</t>
   </si>
   <si>
-    <t>Period during which the qualification is valid.</t>
-  </si>
-  <si>
-    <t>Qualifications are often for a limited period of time, and can be revoked.</t>
-  </si>
-  <si>
     <t>Practitioner.qualification:narcoticPrescriptionLicenseNumber.issuer</t>
-  </si>
-  <si>
-    <t>Organization that regulates and issues the qualification.</t>
   </si>
   <si>
     <t>Practitioner.qualification:medicalRegistrationNumber</t>
@@ -2093,7 +2071,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="107.3984375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="102.6171875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="50.953125" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="52.3828125" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
@@ -3502,7 +3480,7 @@
         <v>78</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K13" t="s" s="2">
         <v>168</v>
@@ -3575,19 +3553,19 @@
         <v>80</v>
       </c>
       <c r="AI13" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ13" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK13" t="s" s="2">
         <v>173</v>
       </c>
-      <c r="AJ13" t="s" s="2">
+      <c r="AL13" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="AK13" t="s" s="2">
+      <c r="AM13" t="s" s="2">
         <v>175</v>
-      </c>
-      <c r="AL13" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="AM13" t="s" s="2">
-        <v>177</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>78</v>
@@ -3595,10 +3573,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3621,19 +3599,19 @@
         <v>91</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="L14" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="M14" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="L14" t="s" s="2">
+      <c r="N14" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="M14" t="s" s="2">
+      <c r="O14" t="s" s="2">
         <v>181</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="O14" t="s" s="2">
-        <v>183</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>78</v>
@@ -3682,7 +3660,7 @@
         <v>78</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>79</v>
@@ -3697,13 +3675,13 @@
         <v>102</v>
       </c>
       <c r="AK14" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="AL14" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="AM14" t="s" s="2">
         <v>184</v>
-      </c>
-      <c r="AL14" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="AM14" t="s" s="2">
-        <v>186</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>78</v>
@@ -3711,10 +3689,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3740,10 +3718,10 @@
         <v>92</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -3794,7 +3772,7 @@
         <v>78</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>79</v>
@@ -3812,7 +3790,7 @@
         <v>78</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>78</v>
@@ -3823,10 +3801,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3855,7 +3833,7 @@
         <v>138</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="N16" t="s" s="2">
         <v>140</v>
@@ -3896,19 +3874,19 @@
         <v>78</v>
       </c>
       <c r="AB16" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE16" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="AC16" t="s" s="2">
+      <c r="AF16" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>197</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
@@ -3926,7 +3904,7 @@
         <v>78</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>78</v>
@@ -3937,10 +3915,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3966,13 +3944,13 @@
         <v>110</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="M17" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="N17" t="s" s="2">
         <v>199</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>201</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3998,11 +3976,11 @@
         <v>78</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="Y17" s="2"/>
       <c r="Z17" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>78</v>
@@ -4020,7 +3998,7 @@
         <v>78</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -4029,19 +4007,19 @@
         <v>90</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="AJ17" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK17" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="AL17" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="AM17" t="s" s="2">
         <v>206</v>
-      </c>
-      <c r="AL17" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="AM17" t="s" s="2">
-        <v>208</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>78</v>
@@ -4049,10 +4027,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4075,19 +4053,19 @@
         <v>91</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="L18" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="O18" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>214</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>78</v>
@@ -4136,7 +4114,7 @@
         <v>78</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
@@ -4151,13 +4129,13 @@
         <v>102</v>
       </c>
       <c r="AK18" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AL18" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="AM18" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="AL18" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="AM18" t="s" s="2">
-        <v>218</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>78</v>
@@ -4165,10 +4143,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4194,16 +4172,16 @@
         <v>110</v>
       </c>
       <c r="L19" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="M19" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="N19" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="O19" t="s" s="2">
         <v>221</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>223</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>78</v>
@@ -4228,11 +4206,11 @@
         <v>78</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="Y19" s="2"/>
       <c r="Z19" t="s" s="2">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>78</v>
@@ -4250,7 +4228,7 @@
         <v>78</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
@@ -4265,13 +4243,13 @@
         <v>102</v>
       </c>
       <c r="AK19" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="AL19" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="AM19" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="AL19" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="AM19" t="s" s="2">
-        <v>228</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>78</v>
@@ -4279,10 +4257,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4305,16 +4283,16 @@
         <v>91</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>231</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>233</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4364,7 +4342,7 @@
         <v>78</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -4379,10 +4357,10 @@
         <v>102</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>78</v>
@@ -4393,10 +4371,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4419,16 +4397,16 @@
         <v>91</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="L21" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="M21" t="s" s="2">
         <v>236</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="N21" t="s" s="2">
         <v>237</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>239</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4478,7 +4456,7 @@
         <v>78</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -4496,10 +4474,10 @@
         <v>134</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>78</v>
@@ -4507,10 +4485,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4533,19 +4511,19 @@
         <v>91</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="L22" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="N22" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="M22" t="s" s="2">
+      <c r="O22" t="s" s="2">
         <v>246</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>248</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>78</v>
@@ -4594,7 +4572,7 @@
         <v>78</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -4609,13 +4587,13 @@
         <v>102</v>
       </c>
       <c r="AK22" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AL22" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="AM22" t="s" s="2">
         <v>249</v>
-      </c>
-      <c r="AL22" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="AM22" t="s" s="2">
-        <v>251</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>78</v>
@@ -4623,10 +4601,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4652,10 +4630,10 @@
         <v>92</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4706,7 +4684,7 @@
         <v>78</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -4724,7 +4702,7 @@
         <v>78</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>78</v>
@@ -4735,10 +4713,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4767,7 +4745,7 @@
         <v>138</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="N24" t="s" s="2">
         <v>140</v>
@@ -4808,19 +4786,19 @@
         <v>78</v>
       </c>
       <c r="AB24" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="AC24" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="AD24" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE24" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="AC24" t="s" s="2">
+      <c r="AF24" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="AD24" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE24" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="AF24" t="s" s="2">
-        <v>197</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -4838,7 +4816,7 @@
         <v>78</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>78</v>
@@ -4849,10 +4827,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4878,16 +4856,16 @@
         <v>110</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="M25" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="N25" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="O25" t="s" s="2">
         <v>256</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>258</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>78</v>
@@ -4900,43 +4878,43 @@
         <v>78</v>
       </c>
       <c r="T25" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="U25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X25" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="Y25" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="Z25" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="U25" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V25" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W25" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X25" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="Y25" t="s" s="2">
+      <c r="AA25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF25" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="Z25" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="AA25" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB25" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC25" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD25" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE25" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF25" t="s" s="2">
-        <v>262</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -4951,13 +4929,13 @@
         <v>102</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>78</v>
@@ -4965,10 +4943,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4994,13 +4972,13 @@
         <v>110</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="M26" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="N26" t="s" s="2">
         <v>266</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -5014,43 +4992,43 @@
         <v>78</v>
       </c>
       <c r="T26" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="U26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X26" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="Y26" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="Z26" t="s" s="2">
         <v>269</v>
       </c>
-      <c r="U26" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V26" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W26" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X26" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="Y26" t="s" s="2">
+      <c r="AA26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF26" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="Z26" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="AA26" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB26" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC26" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD26" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE26" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF26" t="s" s="2">
-        <v>272</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -5065,10 +5043,10 @@
         <v>102</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>78</v>
@@ -5079,10 +5057,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5105,19 +5083,19 @@
         <v>91</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="N27" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="O27" t="s" s="2">
         <v>276</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>278</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>78</v>
@@ -5130,7 +5108,7 @@
         <v>78</v>
       </c>
       <c r="T27" t="s" s="2">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="U27" t="s" s="2">
         <v>78</v>
@@ -5166,7 +5144,7 @@
         <v>78</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -5181,10 +5159,10 @@
         <v>102</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>78</v>
@@ -5195,10 +5173,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5221,16 +5199,16 @@
         <v>91</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="M28" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="N28" t="s" s="2">
         <v>284</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>286</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5244,7 +5222,7 @@
         <v>78</v>
       </c>
       <c r="T28" t="s" s="2">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="U28" t="s" s="2">
         <v>78</v>
@@ -5280,7 +5258,7 @@
         <v>78</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -5295,13 +5273,13 @@
         <v>102</v>
       </c>
       <c r="AK28" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="AL28" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="AM28" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="AL28" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="AM28" t="s" s="2">
-        <v>291</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>78</v>
@@ -5309,14 +5287,14 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -5335,16 +5313,16 @@
         <v>91</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="M29" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="N29" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>296</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5358,7 +5336,7 @@
         <v>78</v>
       </c>
       <c r="T29" t="s" s="2">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="U29" t="s" s="2">
         <v>78</v>
@@ -5394,7 +5372,7 @@
         <v>78</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -5409,13 +5387,13 @@
         <v>102</v>
       </c>
       <c r="AK29" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="AL29" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="AM29" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="AL29" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="AM29" t="s" s="2">
-        <v>301</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>78</v>
@@ -5423,14 +5401,14 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -5449,16 +5427,16 @@
         <v>91</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="M30" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="N30" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>306</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5472,7 +5450,7 @@
         <v>78</v>
       </c>
       <c r="T30" t="s" s="2">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="U30" t="s" s="2">
         <v>78</v>
@@ -5508,7 +5486,7 @@
         <v>78</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -5523,10 +5501,10 @@
         <v>102</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>78</v>
@@ -5537,14 +5515,14 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -5563,16 +5541,16 @@
         <v>91</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="M31" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="N31" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>315</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5622,7 +5600,7 @@
         <v>78</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5637,13 +5615,13 @@
         <v>102</v>
       </c>
       <c r="AK31" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="AL31" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="AM31" t="s" s="2">
         <v>317</v>
-      </c>
-      <c r="AL31" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="AM31" t="s" s="2">
-        <v>319</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>78</v>
@@ -5651,14 +5629,14 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5677,16 +5655,16 @@
         <v>91</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="M32" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="N32" t="s" s="2">
         <v>322</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>324</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5700,7 +5678,7 @@
         <v>78</v>
       </c>
       <c r="T32" t="s" s="2">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="U32" t="s" s="2">
         <v>78</v>
@@ -5736,7 +5714,7 @@
         <v>78</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -5751,13 +5729,13 @@
         <v>102</v>
       </c>
       <c r="AK32" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="AL32" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="AM32" t="s" s="2">
         <v>327</v>
-      </c>
-      <c r="AL32" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="AM32" t="s" s="2">
-        <v>329</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>78</v>
@@ -5765,10 +5743,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5791,16 +5769,16 @@
         <v>91</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="M33" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="N33" t="s" s="2">
         <v>331</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>333</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5850,7 +5828,7 @@
         <v>78</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -5865,13 +5843,13 @@
         <v>102</v>
       </c>
       <c r="AK33" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="AL33" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="AM33" t="s" s="2">
         <v>335</v>
-      </c>
-      <c r="AL33" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="AM33" t="s" s="2">
-        <v>337</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>78</v>
@@ -5879,10 +5857,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5905,19 +5883,19 @@
         <v>91</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="M34" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="O34" t="s" s="2">
         <v>339</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>341</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>78</v>
@@ -5930,7 +5908,7 @@
         <v>78</v>
       </c>
       <c r="T34" t="s" s="2">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="U34" t="s" s="2">
         <v>78</v>
@@ -5966,7 +5944,7 @@
         <v>78</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -5981,13 +5959,13 @@
         <v>102</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>78</v>
@@ -5995,10 +5973,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6024,14 +6002,14 @@
         <v>110</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>78</v>
@@ -6056,13 +6034,13 @@
         <v>78</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>78</v>
@@ -6080,7 +6058,7 @@
         <v>78</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -6095,13 +6073,13 @@
         <v>102</v>
       </c>
       <c r="AK35" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="AL35" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="AM35" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="AL35" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="AM35" t="s" s="2">
-        <v>353</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>78</v>
@@ -6109,10 +6087,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6135,17 +6113,17 @@
         <v>91</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>78</v>
@@ -6194,7 +6172,7 @@
         <v>78</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -6209,13 +6187,13 @@
         <v>102</v>
       </c>
       <c r="AK36" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="AL36" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="AM36" t="s" s="2">
         <v>358</v>
-      </c>
-      <c r="AL36" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="AM36" t="s" s="2">
-        <v>360</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>78</v>
@@ -6223,10 +6201,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6249,19 +6227,19 @@
         <v>78</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="L37" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="N37" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="O37" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>366</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>78</v>
@@ -6310,7 +6288,7 @@
         <v>78</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -6328,10 +6306,10 @@
         <v>78</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>78</v>
@@ -6339,10 +6317,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6365,16 +6343,16 @@
         <v>78</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="L38" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>373</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6412,17 +6390,17 @@
         <v>78</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="AC38" s="2"/>
       <c r="AD38" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -6434,16 +6412,16 @@
         <v>78</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>174</v>
+        <v>373</v>
       </c>
       <c r="AK38" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="AL38" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="AL38" t="s" s="2">
+      <c r="AM38" t="s" s="2">
         <v>376</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>377</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>78</v>
@@ -6451,10 +6429,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6477,13 +6455,13 @@
         <v>78</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6534,7 +6512,7 @@
         <v>78</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6552,7 +6530,7 @@
         <v>78</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>78</v>
@@ -6563,10 +6541,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6595,7 +6573,7 @@
         <v>138</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="N40" t="s" s="2">
         <v>140</v>
@@ -6648,7 +6626,7 @@
         <v>78</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -6666,7 +6644,7 @@
         <v>78</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>78</v>
@@ -6677,14 +6655,14 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -6706,10 +6684,10 @@
         <v>137</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>382</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>383</v>
       </c>
       <c r="N41" t="s" s="2">
         <v>140</v>
@@ -6764,7 +6742,7 @@
         <v>78</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -6793,10 +6771,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6822,16 +6800,16 @@
         <v>149</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="N42" t="s" s="2">
+      <c r="O42" t="s" s="2">
         <v>388</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>389</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>78</v>
@@ -6880,7 +6858,7 @@
         <v>78</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -6898,7 +6876,7 @@
         <v>78</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>78</v>
@@ -6909,10 +6887,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6935,16 +6913,16 @@
         <v>78</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="L43" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="M43" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>395</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6970,14 +6948,14 @@
         <v>78</v>
       </c>
       <c r="X43" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="Y43" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="Y43" t="s" s="2">
+      <c r="Z43" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="Z43" t="s" s="2">
-        <v>398</v>
-      </c>
       <c r="AA43" t="s" s="2">
         <v>78</v>
       </c>
@@ -6994,7 +6972,7 @@
         <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>90</v>
@@ -7012,10 +6990,10 @@
         <v>78</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>78</v>
@@ -7023,10 +7001,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7049,19 +7027,19 @@
         <v>78</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="N44" t="s" s="2">
+      <c r="O44" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>404</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>78</v>
@@ -7110,7 +7088,7 @@
         <v>78</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -7128,10 +7106,10 @@
         <v>78</v>
       </c>
       <c r="AL44" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="AM44" t="s" s="2">
         <v>405</v>
-      </c>
-      <c r="AM44" t="s" s="2">
-        <v>406</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>78</v>
@@ -7139,10 +7117,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7165,16 +7143,16 @@
         <v>78</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="L45" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="L45" t="s" s="2">
+      <c r="M45" t="s" s="2">
         <v>409</v>
       </c>
-      <c r="M45" t="s" s="2">
+      <c r="N45" t="s" s="2">
         <v>410</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>411</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7224,7 +7202,7 @@
         <v>78</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -7242,7 +7220,7 @@
         <v>78</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>78</v>
@@ -7253,13 +7231,13 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="C46" t="s" s="2">
         <v>413</v>
-      </c>
-      <c r="B46" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="C46" t="s" s="2">
-        <v>414</v>
       </c>
       <c r="D46" t="s" s="2">
         <v>78</v>
@@ -7269,25 +7247,25 @@
         <v>79</v>
       </c>
       <c r="G46" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="H46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K46" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="L46" t="s" s="2">
         <v>415</v>
       </c>
-      <c r="H46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K46" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="L46" t="s" s="2">
+      <c r="M46" t="s" s="2">
         <v>416</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>417</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7338,7 +7316,7 @@
         <v>78</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -7350,16 +7328,16 @@
         <v>78</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>174</v>
+        <v>373</v>
       </c>
       <c r="AK46" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="AL46" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="AL46" t="s" s="2">
+      <c r="AM46" t="s" s="2">
         <v>376</v>
-      </c>
-      <c r="AM46" t="s" s="2">
-        <v>377</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>78</v>
@@ -7367,10 +7345,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7393,13 +7371,13 @@
         <v>78</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7450,7 +7428,7 @@
         <v>78</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7468,7 +7446,7 @@
         <v>78</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>78</v>
@@ -7479,10 +7457,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7511,7 +7489,7 @@
         <v>138</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="N48" t="s" s="2">
         <v>140</v>
@@ -7564,7 +7542,7 @@
         <v>78</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7582,7 +7560,7 @@
         <v>78</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>78</v>
@@ -7593,14 +7571,14 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7622,10 +7600,10 @@
         <v>137</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>382</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>383</v>
       </c>
       <c r="N49" t="s" s="2">
         <v>140</v>
@@ -7680,7 +7658,7 @@
         <v>78</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -7709,10 +7687,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7738,14 +7716,16 @@
         <v>149</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="N50" s="2"/>
+        <v>386</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>387</v>
+      </c>
       <c r="O50" t="s" s="2">
-        <v>424</v>
+        <v>388</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>78</v>
@@ -7794,7 +7774,7 @@
         <v>78</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -7812,7 +7792,7 @@
         <v>78</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>78</v>
@@ -7823,10 +7803,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7852,10 +7832,10 @@
         <v>92</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7906,7 +7886,7 @@
         <v>78</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -7924,7 +7904,7 @@
         <v>78</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>78</v>
@@ -7935,10 +7915,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7967,7 +7947,7 @@
         <v>138</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="N52" t="s" s="2">
         <v>140</v>
@@ -8008,19 +7988,19 @@
         <v>78</v>
       </c>
       <c r="AB52" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE52" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="AC52" t="s" s="2">
+      <c r="AF52" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="AD52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE52" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="AF52" t="s" s="2">
-        <v>197</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -8038,7 +8018,7 @@
         <v>78</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>78</v>
@@ -8049,10 +8029,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8078,16 +8058,16 @@
         <v>110</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="O53" t="s" s="2">
         <v>431</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>434</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>78</v>
@@ -8112,11 +8092,11 @@
         <v>78</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="Y53" s="2"/>
       <c r="Z53" t="s" s="2">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>78</v>
@@ -8134,7 +8114,7 @@
         <v>78</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -8152,7 +8132,7 @@
         <v>134</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>78</v>
@@ -8163,10 +8143,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8189,19 +8169,19 @@
         <v>91</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="O54" t="s" s="2">
         <v>440</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>443</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>78</v>
@@ -8226,11 +8206,11 @@
         <v>78</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="Y54" s="2"/>
       <c r="Z54" t="s" s="2">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>78</v>
@@ -8248,7 +8228,7 @@
         <v>78</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8263,10 +8243,10 @@
         <v>102</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>78</v>
@@ -8277,10 +8257,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8306,16 +8286,16 @@
         <v>104</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="O55" t="s" s="2">
         <v>450</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>453</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>78</v>
@@ -8328,7 +8308,7 @@
         <v>78</v>
       </c>
       <c r="T55" t="s" s="2">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="U55" t="s" s="2">
         <v>78</v>
@@ -8364,7 +8344,7 @@
         <v>78</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8379,13 +8359,13 @@
         <v>102</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>78</v>
@@ -8393,10 +8373,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8419,16 +8399,16 @@
         <v>91</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8442,7 +8422,7 @@
         <v>78</v>
       </c>
       <c r="T56" t="s" s="2">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="U56" t="s" s="2">
         <v>78</v>
@@ -8478,7 +8458,7 @@
         <v>78</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8493,13 +8473,13 @@
         <v>102</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>78</v>
@@ -8507,10 +8487,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8533,13 +8513,13 @@
         <v>91</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8590,7 +8570,7 @@
         <v>78</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -8605,13 +8585,13 @@
         <v>102</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>78</v>
@@ -8619,10 +8599,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8645,16 +8625,16 @@
         <v>91</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="N58" t="s" s="2">
         <v>477</v>
-      </c>
-      <c r="L58" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>480</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8704,7 +8684,7 @@
         <v>78</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8719,13 +8699,13 @@
         <v>102</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>78</v>
@@ -8733,10 +8713,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8759,15 +8739,17 @@
         <v>78</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="L59" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="L59" t="s" s="2">
+      <c r="M59" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="M59" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="N59" s="2"/>
+      <c r="N59" t="s" s="2">
+        <v>394</v>
+      </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>78</v>
@@ -8777,7 +8759,7 @@
         <v>78</v>
       </c>
       <c r="S59" t="s" s="2">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="T59" t="s" s="2">
         <v>78</v>
@@ -8792,11 +8774,11 @@
         <v>78</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="Y59" s="2"/>
       <c r="Z59" t="s" s="2">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>78</v>
@@ -8814,7 +8796,7 @@
         <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>90</v>
@@ -8832,10 +8814,10 @@
         <v>78</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>78</v>
@@ -8843,10 +8825,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8869,17 +8851,19 @@
         <v>78</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="M60" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="N60" s="2"/>
+      <c r="N60" t="s" s="2">
+        <v>402</v>
+      </c>
       <c r="O60" t="s" s="2">
-        <v>491</v>
+        <v>403</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>78</v>
@@ -8928,7 +8912,7 @@
         <v>78</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -8946,10 +8930,10 @@
         <v>78</v>
       </c>
       <c r="AL60" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="AM60" t="s" s="2">
         <v>405</v>
-      </c>
-      <c r="AM60" t="s" s="2">
-        <v>406</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>78</v>
@@ -8957,10 +8941,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8983,15 +8967,17 @@
         <v>78</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>409</v>
       </c>
-      <c r="M61" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="N61" s="2"/>
+      <c r="N61" t="s" s="2">
+        <v>410</v>
+      </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>78</v>
@@ -9040,7 +9026,7 @@
         <v>78</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -9058,7 +9044,7 @@
         <v>78</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>78</v>
@@ -9069,13 +9055,13 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C62" t="s" s="2">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="D62" t="s" s="2">
         <v>78</v>
@@ -9097,13 +9083,13 @@
         <v>78</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>416</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>417</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9154,7 +9140,7 @@
         <v>78</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -9166,16 +9152,16 @@
         <v>78</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>174</v>
+        <v>373</v>
       </c>
       <c r="AK62" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="AL62" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="AL62" t="s" s="2">
+      <c r="AM62" t="s" s="2">
         <v>376</v>
-      </c>
-      <c r="AM62" t="s" s="2">
-        <v>377</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>78</v>
@@ -9183,10 +9169,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>496</v>
+        <v>489</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9209,13 +9195,13 @@
         <v>78</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9266,7 +9252,7 @@
         <v>78</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -9284,7 +9270,7 @@
         <v>78</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>78</v>
@@ -9295,10 +9281,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9327,7 +9313,7 @@
         <v>138</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="N64" t="s" s="2">
         <v>140</v>
@@ -9380,7 +9366,7 @@
         <v>78</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -9398,7 +9384,7 @@
         <v>78</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>78</v>
@@ -9409,14 +9395,14 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -9438,10 +9424,10 @@
         <v>137</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>382</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>383</v>
       </c>
       <c r="N65" t="s" s="2">
         <v>140</v>
@@ -9496,7 +9482,7 @@
         <v>78</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -9525,10 +9511,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>499</v>
+        <v>492</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9554,14 +9540,16 @@
         <v>149</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>500</v>
+        <v>493</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="N66" s="2"/>
+        <v>386</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>387</v>
+      </c>
       <c r="O66" t="s" s="2">
-        <v>424</v>
+        <v>388</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>78</v>
@@ -9610,7 +9598,7 @@
         <v>78</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -9628,7 +9616,7 @@
         <v>78</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>78</v>
@@ -9639,10 +9627,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>501</v>
+        <v>494</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9668,10 +9656,10 @@
         <v>92</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9722,7 +9710,7 @@
         <v>78</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -9740,7 +9728,7 @@
         <v>78</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>78</v>
@@ -9751,10 +9739,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>502</v>
+        <v>495</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9783,7 +9771,7 @@
         <v>138</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="N68" t="s" s="2">
         <v>140</v>
@@ -9824,19 +9812,19 @@
         <v>78</v>
       </c>
       <c r="AB68" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE68" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="AC68" t="s" s="2">
+      <c r="AF68" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="AD68" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE68" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="AF68" t="s" s="2">
-        <v>197</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -9854,7 +9842,7 @@
         <v>78</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>78</v>
@@ -9865,10 +9853,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>503</v>
+        <v>496</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9894,16 +9882,16 @@
         <v>110</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="O69" t="s" s="2">
         <v>431</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>434</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>78</v>
@@ -9928,11 +9916,11 @@
         <v>78</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="Y69" s="2"/>
       <c r="Z69" t="s" s="2">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>78</v>
@@ -9950,7 +9938,7 @@
         <v>78</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -9968,7 +9956,7 @@
         <v>134</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>78</v>
@@ -9979,10 +9967,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>504</v>
+        <v>497</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10005,19 +9993,19 @@
         <v>91</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="O70" t="s" s="2">
         <v>440</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>443</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>78</v>
@@ -10042,11 +10030,11 @@
         <v>78</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="Y70" s="2"/>
       <c r="Z70" t="s" s="2">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>78</v>
@@ -10064,7 +10052,7 @@
         <v>78</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -10079,10 +10067,10 @@
         <v>102</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>78</v>
@@ -10093,10 +10081,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>505</v>
+        <v>498</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10122,29 +10110,29 @@
         <v>104</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>506</v>
+        <v>499</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>508</v>
+        <v>501</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q71" s="2"/>
       <c r="R71" t="s" s="2">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="S71" t="s" s="2">
         <v>78</v>
       </c>
       <c r="T71" t="s" s="2">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="U71" t="s" s="2">
         <v>78</v>
@@ -10180,7 +10168,7 @@
         <v>78</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -10195,13 +10183,13 @@
         <v>102</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>78</v>
@@ -10209,10 +10197,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10235,16 +10223,16 @@
         <v>91</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>500</v>
+        <v>493</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>500</v>
+        <v>493</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10258,7 +10246,7 @@
         <v>78</v>
       </c>
       <c r="T72" t="s" s="2">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="U72" t="s" s="2">
         <v>78</v>
@@ -10294,7 +10282,7 @@
         <v>78</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10309,13 +10297,13 @@
         <v>102</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>78</v>
@@ -10323,10 +10311,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>511</v>
+        <v>504</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10349,13 +10337,13 @@
         <v>91</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10406,7 +10394,7 @@
         <v>78</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -10421,13 +10409,13 @@
         <v>102</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>78</v>
@@ -10435,10 +10423,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10461,16 +10449,16 @@
         <v>91</v>
       </c>
       <c r="K74" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="N74" t="s" s="2">
         <v>477</v>
-      </c>
-      <c r="L74" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>480</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -10520,7 +10508,7 @@
         <v>78</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -10535,13 +10523,13 @@
         <v>102</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>78</v>
@@ -10549,10 +10537,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10575,15 +10563,17 @@
         <v>78</v>
       </c>
       <c r="K75" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="L75" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="L75" t="s" s="2">
+      <c r="M75" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="M75" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="N75" s="2"/>
+      <c r="N75" t="s" s="2">
+        <v>394</v>
+      </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>78</v>
@@ -10593,7 +10583,7 @@
         <v>78</v>
       </c>
       <c r="S75" t="s" s="2">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="T75" t="s" s="2">
         <v>78</v>
@@ -10608,11 +10598,11 @@
         <v>78</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="Y75" s="2"/>
       <c r="Z75" t="s" s="2">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>78</v>
@@ -10630,7 +10620,7 @@
         <v>78</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>90</v>
@@ -10648,10 +10638,10 @@
         <v>78</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>78</v>
@@ -10659,10 +10649,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10685,17 +10675,19 @@
         <v>78</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="L76" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="M76" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="M76" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="N76" s="2"/>
+      <c r="N76" t="s" s="2">
+        <v>402</v>
+      </c>
       <c r="O76" t="s" s="2">
-        <v>491</v>
+        <v>403</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>78</v>
@@ -10744,7 +10736,7 @@
         <v>78</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
@@ -10762,10 +10754,10 @@
         <v>78</v>
       </c>
       <c r="AL76" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="AM76" t="s" s="2">
         <v>405</v>
-      </c>
-      <c r="AM76" t="s" s="2">
-        <v>406</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>78</v>
@@ -10773,10 +10765,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>516</v>
+        <v>509</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10799,15 +10791,17 @@
         <v>78</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="L77" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="M77" t="s" s="2">
         <v>409</v>
       </c>
-      <c r="M77" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="N77" s="2"/>
+      <c r="N77" t="s" s="2">
+        <v>410</v>
+      </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>78</v>
@@ -10856,7 +10850,7 @@
         <v>78</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
@@ -10874,7 +10868,7 @@
         <v>78</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>78</v>
@@ -10885,10 +10879,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10911,19 +10905,19 @@
         <v>78</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>519</v>
+        <v>512</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>520</v>
+        <v>513</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>521</v>
+        <v>514</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>78</v>
@@ -10972,7 +10966,7 @@
         <v>78</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
@@ -10987,13 +10981,13 @@
         <v>102</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>522</v>
+        <v>515</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>524</v>
+        <v>517</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>78</v>

--- a/jpcore-r4b/develop/StructureDefinition-jp-practitioner.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-practitioner.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-dev</t>
+    <t>2.0.0-dev-temp</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-31</t>
+    <t>2024-12-30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -90,7 +90,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>
@@ -371,7 +371,7 @@
     <t>IETF language tag</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.3.0</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -1218,7 +1218,7 @@
 麻薬施用者免許番号の場合のsystemはFixed Valueの urn:oid:1.2.392.100495.20.3.32.1[都道府県番号] を使用する。  
 ( 頭に1をつけて末尾3桁で表現する。これは北海道などの場合、都道府県番号は01になるが、OIDでは先頭が0は許可されていないため、頭に1をつけて3桁で表現する)  
 つまり麻薬施用者免許番号を発行した都道府県ごとにsystemも異なる値となる。  
-医籍登録番号のsystemはFixed Valueの urn:oid:1.2.392.100495.20.3.31 を使用する。</t>
+医籍登録番号のsystemはFixed Valueの http://jpfhir.jp/fhir/core/mhlw/IdSystem/medicalRegistrationNumber を使用する。</t>
   </si>
   <si>
     <t xml:space="preserve">value:code}
@@ -1273,7 +1273,7 @@
     <t>【JP Core仕様】identifierには資格番号を入力する。  
 Codeは、v2 table 0360が例としてのっている。0360は、USER-DEFINED TABLES であるため、適切なCodeがなければ追加できる。  
 Periodにはその資格の開始日・終了日を入力する。（例：麻薬資格者の有効期限等の格納）  
-医籍登録番号　Practitioner.qualification.identifier　urn:oid:1.2.392.100495.20.3.31  
+医籍登録番号　Practitioner.qualification.identifier　http://jpfhir.jp/fhir/core/mhlw/IdSystem/medicalRegistrationNumber  
 麻薬施用者番号　Practitioner.qualification.identifier　urn:oid:1.2.392.100495.20.3.32.都道府県OID番号  
 　　（都道府県OID番号は、都道府県番号2桁の先頭に１をつけた3桁の番号）</t>
   </si>
@@ -1322,7 +1322,7 @@
   </si>
   <si>
     <t>使用のコンテキストは、範囲全体が適用されるか（例：「患者はこの時間範囲で病院の入院患者であった」）、範囲内の1つの値が適用されるか（例：「この2つの時間の間に患者に与える」）を指定する。  
-期間は、期間(経過時間の尺度)には使用されない。[Duration](http://hl7.org/fhir/R4B/datatypes.html#Duration)を参照のこと。</t>
+期間は、期間(経過時間の尺度)には使用されない。[Duration](http://hl7.org/fhir/R4/datatypes.html#Duration)を参照のこと。</t>
   </si>
   <si>
     <t>資格は期間限定のものが多く、取り消されることもある。</t>
@@ -1337,7 +1337,7 @@
     <t>Practitioner.qualification.issuer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.3.0)
 </t>
   </si>
   <si>
@@ -1443,7 +1443,7 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.3.0</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -1677,7 +1677,7 @@
     <t>Identifier.system is always case sensitive.</t>
   </si>
   <si>
-    <t>urn:oid:1.2.392.100495.20.3.31</t>
+    <t>http://jpfhir.jp/fhir/core/mhlw/IdSystem/medicalRegistrationNumber</t>
   </si>
   <si>
     <t>Practitioner.qualification:medicalRegistrationNumber.identifier.value</t>
@@ -2034,17 +2034,17 @@
   <dimension ref="A1:AN78"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="75.0546875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="41.8671875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="33.61328125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="64.34765625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="35.89453125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="28.8203125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="70.1796875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="60.1640625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2053,26 +2053,26 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="39.97265625" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="58.06640625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="60.75390625" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="34.859375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="34.26953125" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="49.78125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="52.0859375" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="29.88671875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="107.3984375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="102.6171875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="52.3828125" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="92.07421875" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="87.9765625" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="44.90625" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="31.65234375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/jpcore-r4b/develop/StructureDefinition-jp-practitioner.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-practitioner.xlsx
@@ -1322,7 +1322,7 @@
   </si>
   <si>
     <t>使用のコンテキストは、範囲全体が適用されるか（例：「患者はこの時間範囲で病院の入院患者であった」）、範囲内の1つの値が適用されるか（例：「この2つの時間の間に患者に与える」）を指定する。  
-期間は、期間(経過時間の尺度)には使用されない。[Duration](http://hl7.org/fhir/R4/datatypes.html#Duration)を参照のこと。</t>
+期間は、期間(経過時間の尺度)には使用されない。[Duration](http://hl7.org/fhir/R4B/datatypes.html#Duration)を参照のこと。</t>
   </si>
   <si>
     <t>資格は期間限定のものが多く、取り消されることもある。</t>

--- a/jpcore-r4b/develop/StructureDefinition-jp-practitioner.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-practitioner.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-dev-temp</t>
+    <t>2.0.0-dev</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4b/develop/StructureDefinition-jp-practitioner.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-practitioner.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2859" uniqueCount="518">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2859" uniqueCount="525">
   <si>
     <t>Property</t>
   </si>
@@ -269,8 +269,8 @@
 医療の提供に直接または間接的に関与する者をいう。</t>
   </si>
   <si>
-    <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where(((id.exists() and ('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url)))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(uri) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
+    <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where(((id.exists() and ('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url)))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(uri) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が存在することが望ましい / A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>PRD (as one example)</t>
@@ -298,13 +298,13 @@
 </t>
   </si>
   <si>
-    <t>Logical id of this artifact</t>
-  </si>
-  <si>
-    <t>The logical id of the resource, as used in the URL for the resource. Once assigned, this value never changes.</t>
-  </si>
-  <si>
-    <t>The only time that a resource does not have an id is when it is being submitted to the server using a create operation.</t>
+    <t>このアーティファクトの論理ID / Logical id of this artifact</t>
+  </si>
+  <si>
+    <t>リソースのURLで使用されるリソースの論理ID。割り当てられたら、この値は変更されません。 / The logical id of the resource, as used in the URL for the resource. Once assigned, this value never changes.</t>
+  </si>
+  <si>
+    <t>リソースにIDがないのは、IDが作成操作を使用してサーバーに送信されている場合です。 / The only time that a resource does not have an id is when it is being submitted to the server using a create operation.</t>
   </si>
   <si>
     <t>Resource.id</t>
@@ -317,16 +317,16 @@
 </t>
   </si>
   <si>
-    <t>Metadata about the resource</t>
-  </si>
-  <si>
-    <t>The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
+    <t>リソースに関するMetadata / Metadata about the resource</t>
+  </si>
+  <si>
+    <t>リソースに関するMetadata。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
   </si>
   <si>
     <t>Resource.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
@@ -337,13 +337,13 @@
 </t>
   </si>
   <si>
-    <t>A set of rules under which this content was created</t>
-  </si>
-  <si>
-    <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
-  </si>
-  <si>
-    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
+    <t>このコンテンツが作成されたルールのセット / A set of rules under which this content was created</t>
+  </si>
+  <si>
+    <t>リソースが構築されたときに従った一連のルールへの参照。コンテンツの処理時に理解する必要があります。多くの場合、これは他のプロファイルなどとともに特別なルールを定義する実装ガイドへの参照です。 / A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
+  </si>
+  <si>
+    <t>このルールセットを主張することは、コンテンツが限られた取引パートナーのセットによってのみ理解されることを制限します。これにより、本質的に長期的にデータの有用性が制限されます。ただし、既存の健康エコシステムは非常に破壊されており、一般的に計算可能な意味でデータを定義、収集、交換する準備ができていません。可能な限り、実装者や仕様ライターはこの要素の使用を避ける必要があります。多くの場合、使用する場合、URLは、これらの特別なルールを他のプロファイル、バリューセットなどとともに叙述(Narative)の一部として定義する実装ガイドへの参照です。 / Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
   </si>
   <si>
     <t>Resource.implicitRules</t>
@@ -356,19 +356,19 @@
 </t>
   </si>
   <si>
-    <t>Language of the resource content</t>
-  </si>
-  <si>
-    <t>The base language in which the resource is written.</t>
-  </si>
-  <si>
-    <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
+    <t>リソースコンテンツの言語 / Language of the resource content</t>
+  </si>
+  <si>
+    <t>リソースが書かれている基本言語。 / The base language in which the resource is written.</t>
+  </si>
+  <si>
+    <t>言語は、インデックス作成とアクセシビリティをサポートするために提供されます（通常、テキストから音声までのサービスなどのサービスが言語タグを使用します）。叙述(Narative)のHTML言語タグは、叙述(Narative)に適用されます。リソース上の言語タグを使用して、リソース内のデータから生成された他のプレゼンテーションの言語を指定できます。すべてのコンテンツが基本言語である必要はありません。リソース。言語は、叙述(Narative)に自動的に適用されると想定されるべきではありません。言語が指定されている場合、HTMLのDIV要素にも指定されている場合（XML：LangとHTML Lang属性の関係については、HTML5のルールを参照してください）。 / Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
   </si>
   <si>
     <t>preferred</t>
   </si>
   <si>
-    <t>IETF language tag</t>
+    <t>IETF言語タグ / IETF language tag</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/languages|4.3.0</t>
@@ -388,13 +388,13 @@
 </t>
   </si>
   <si>
-    <t>Text summary of the resource, for human interpretation</t>
-  </si>
-  <si>
-    <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
-  </si>
-  <si>
-    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
+    <t>人間の解釈のためのリソースのテキスト概要 / Text summary of the resource, for human interpretation</t>
+  </si>
+  <si>
+    <t>リソースの概要を含み、人間へのリソースの内容を表すために使用できる人間の読み取り可能な叙述(Narative)。叙述(Narative)はすべての構造化されたデータをエンコードする必要はありませんが、人間が叙述(Narative)を読むだけで「臨床的に安全」にするために十分な詳細を含める必要があります。リソースの定義は、臨床的安全を確保するために、叙述(Narative)で表現するコンテンツを定義する場合があります。 / A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
+  </si>
+  <si>
+    <t>含まれるリソースには叙述(Narative)がありません。含まれていないリソースには叙述(Narative)が必要です。場合によっては、リソースには、追加の個別のデータがほとんどまたはまったくないテキストのみがあります（すべてのMinoccur = 1要素が満たされている限り）。これは、情報がtext blob (バイナリー ラージ オブジェクト)としてキャプチャされるレガシーシステムからのデータ、またはテキストが生またはナレーションされ、エンコードされた情報が後で追加される場合に必要になる場合があります。 / Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
   </si>
   <si>
     <t>DomainResource.text</t>
@@ -414,19 +414,19 @@
 </t>
   </si>
   <si>
-    <t>Contained, inline Resources</t>
-  </si>
-  <si>
-    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
-  </si>
-  <si>
-    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
+    <t>インラインリソースが含まれています / Contained, inline Resources</t>
+  </si>
+  <si>
+    <t>これらのリソースには、それらを含むリソースを除いて独立した存在はありません - 独立して特定することはできず、独自の独立したトランザクションスコープを持つこともできません。 / These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
+  </si>
+  <si>
+    <t>識別が失われると、コンテンツを適切に識別できる場合は、これを行うべきではありません。含まれるリソースには、メタ要素にプロファイルとタグがある場合がありますが、セキュリティラベルはありません。 / This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
   </si>
   <si>
     <t>DomainResource.contained</t>
   </si>
   <si>
-    <t xml:space="preserve">dom-r4b:Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
+    <t xml:space="preserve">dom-r4b:R4リソース内に新しいR4Bリソースを含めると、インスタンスがR4システムと共有された場合に相互運用性の問題が発生する可能性があります / Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
 </t>
   </si>
   <si>
@@ -444,33 +444,34 @@
 </t>
   </si>
   <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+    <t>実装で定義された追加のコンテンツ / Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>リソースの基本的な定義の一部ではない追加情報を表すために使用できます。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たされる一連の要件があります。 / May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>拡張機能を使用または定義する機関や管轄権に関係なく、アプリケーション、プロジェクト、または標準による拡張機能の使用に関連するスティグマはありません。拡張機能の使用は、FHIR仕様がすべての人にコアレベルのシンプルさを保持できるようにするものです。 / There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
     <t>DomainResource.extension</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>Practitioner.modifierExtension</t>
   </si>
   <si>
-    <t>Extensions that cannot be ignored</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+    <t>無視できない拡張機能 / Extensions that cannot be ignored</t>
+  </si>
+  <si>
+    <t>リソースの基本的な定義の一部ではなく、それを含む要素の理解および/または含有要素の子孫の理解を変更するために使用される場合があります。通常、修飾子要素は否定または資格を提供します。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義することが許可されていますが、拡張機能の定義の一部として満たされる一連の要件があります。アプリケーションの処理リソースは、修飾子拡張機能をチェックする必要があります。
+モディファイア拡張は、リソースまたはdomainResource上の要素の意味を変更してはなりません（修飾軸自体の意味を変更することはできません）。 / May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
+    <t>修飾子拡張機能により、安全に無視できる大部分の拡張機能と明確に区別できるように、安全に無視できない拡張機能が可能になります。これにより、実装者が拡張の存在を禁止する必要性を排除することにより、相互運用性が促進されます。詳細については、[修飾子拡張の定義]（拡張性.html＃modifierextension）を参照してください。 / Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
@@ -524,7 +525,7 @@
 </t>
   </si>
   <si>
-    <t>Whether this practitioner's record is in active use</t>
+    <t>この開業医の記録が積極的に使用されているかどうか / Whether this practitioner's record is in active use</t>
   </si>
   <si>
     <t>この医療従事者の記録がアクティブに使用されているかどうかを示す。</t>
@@ -536,7 +537,7 @@
     <t>医療従事者のレコードを誤って作成してしまったとき、使用しないようにマークできるようにする必要がある。</t>
   </si>
   <si>
-    <t>This resource is generally assumed to be active if no value is provided for the active element</t>
+    <t>このリソースは、アクティブな要素の値が提供されていない場合、一般にアクティブであると想定されています / This resource is generally assumed to be active if no value is provided for the active element</t>
   </si>
   <si>
     <t>./statusCode</t>
@@ -552,7 +553,7 @@
 </t>
   </si>
   <si>
-    <t>The name(s) associated with the practitioner</t>
+    <t>開業医に関連付けられた名前 / The name(s) associated with the practitioner</t>
   </si>
   <si>
     <t>医療従事者の氏名（複数の場合もある）</t>
@@ -613,10 +614,10 @@
     <t>Practitioner.telecom.id</t>
   </si>
   <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+    <t>エレメント相互参照のためのユニークID / Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>リソース内の要素の固有ID（内部参照用）。これは、スペースを含まない任意の文字列値である可能性があります。 / Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
   </si>
   <si>
     <t>Element.id</t>
@@ -628,7 +629,13 @@
     <t>Practitioner.telecom.extension</t>
   </si>
   <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+    <t>実装によって定義される追加コンテンツ / Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>要素の基本的な定義に含まれない追加情報を表すために使用されることがあります。拡張機能の使用を安全かつ管理しやすくするために、定義および使用に適用される厳格なガバナンスのセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たす必要のある要件のセットがあります。 / May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>どのようなアプリケーション、プロジェクト、または標準が拡張機能を使用しているかに関わらず、拡張機能の使用には決して汚名が付くわけではありません - それらを使用または定義する機関または管轄区域に関係なく。拡張機能の使用こそが、FHIR仕様を誰にとっても簡単なコアレベルで維持することを可能にします。 / There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
     <t xml:space="preserve">value:url}
@@ -644,13 +651,17 @@
     <t>Element.extension</t>
   </si>
   <si>
+    <t>ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:extensionまたはvalue[x]のいずれかが必要です。両方ではありません。 / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
     <t>Practitioner.telecom.system</t>
   </si>
   <si>
     <t>phone | fax | email | pager | url | sms | other 【JP_Patient.telecomを参照。】</t>
   </si>
   <si>
-    <t>Telecommunications form for contact point - what communications system is required to make use of the contact.</t>
+    <t>連絡先用通信フォーム - どの通信システムを使用するには接点が必要ですか。 / Telecommunications form for contact point - what communications system is required to make use of the contact.</t>
   </si>
   <si>
     <t>連絡先の種別をValueSet(ContactPointSystem)より選択する。  　- phone : 電話　- fax : Fax 　- email : 電子メール　- pager : ポケットベル　- url : 電話、ファックス、ポケットベル、または電子メールアドレスではなく、URLとして表される連絡先。これはWebサイト、ブログ、Skype、Twitter、Facebookなどのさまざまな機関または個人の連絡先を対象としている。電子メールアドレスには使用しないこと。　- sms : SMSメッセージの送信に使用できる連絡先（携帯電話、一部の固定電話など）  　- other : 電話、Fax、ポケットベル、または電子メールアドレスではなく、URLとして表現できない連絡先。例：内部メールアドレス。これは、URLとして表現できる連絡先（Skype、Twitter、Facebookなど）には使用しないこと。</t>
@@ -669,6 +680,10 @@
 </t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+</t>
+  </si>
+  <si>
     <t>XTN.3</t>
   </si>
   <si>
@@ -685,16 +700,16 @@
 </t>
   </si>
   <si>
-    <t>The actual contact point details</t>
-  </si>
-  <si>
-    <t>The actual contact point details, in a form that is meaningful to the designated communication system (i.e. phone number or email address).</t>
+    <t>実際の連絡先の詳細 / The actual contact point details</t>
+  </si>
+  <si>
+    <t>指定されたコミュニケーションシステムに意味がある形式での実際の連絡先の詳細（電話番号または電子メールアドレス）を提供してください。 / The actual contact point details, in a form that is meaningful to the designated communication system (i.e. phone number or email address).</t>
   </si>
   <si>
     <t>連絡先の番号やメールアドレス</t>
   </si>
   <si>
-    <t>Need to support legacy numbers that are not in a tightly controlled format.</t>
+    <t>厳密に管理された形式でないレガシー番号をサポートする必要がある。 / Need to support legacy numbers that are not in a tightly controlled format.</t>
   </si>
   <si>
     <t>ContactPoint.value</t>
@@ -715,7 +730,7 @@
     <t>home | work | temp | old | mobile - 連絡先の用途等 【JP_Patient.telecomを参照。】</t>
   </si>
   <si>
-    <t>Identifies the purpose for the contact point.</t>
+    <t>接点の目的を特定する。 / Identifies the purpose for the contact point.</t>
   </si>
   <si>
     <t>患者の連絡先の種別をValueSet(ContactPointUse)より選択する。  一時的なものまたは古いものであると明示しない限り、連絡先が最新とみなされる。  
@@ -726,7 +741,7 @@
 　- mobile : モバイル機器</t>
   </si>
   <si>
-    <t>Need to track the way a person uses this contact, so a user can choose which is appropriate for their purpose.</t>
+    <t>人がこの連絡先をどのように使用するかを追跡し、ユーザーが目的に適したものを選択できるようにする必要がある。 / Need to track the way a person uses this contact, so a user can choose which is appropriate for their purpose.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/contact-point-use|4.3.0</t>
@@ -751,10 +766,10 @@
 </t>
   </si>
   <si>
-    <t>Specify preferred order of use (1 = highest)</t>
-  </si>
-  <si>
-    <t>Specifies a preferred order in which to use a set of contacts. ContactPoints with lower rank values are more preferred than those with higher rank values.</t>
+    <t>使用の優先順位を指定してください（1が最も優先度が高い） / Specify preferred order of use (1 = highest)</t>
+  </si>
+  <si>
+    <t>一連のコンタクトを使う上で好ましい順序を指定します。ランク値が低いContactPointsの方が、ランク値が高いものよりも優先されます。 / Specifies a preferred order in which to use a set of contacts. ContactPoints with lower rank values are more preferred than those with higher rank values.</t>
   </si>
   <si>
     <t>連絡先の使用順序（1 = 最高）</t>
@@ -770,10 +785,10 @@
 </t>
   </si>
   <si>
-    <t>Time period when the contact point was/is in use</t>
-  </si>
-  <si>
-    <t>Time period when the contact point was/is in use.</t>
+    <t>コンタクトポイントが使用されている時間帯 / Time period when the contact point was/is in use</t>
+  </si>
+  <si>
+    <t>接点が使用されていた/現在使用中である時間期間 / Time period when the contact point was/is in use.</t>
   </si>
   <si>
     <t>連絡先が使用されていた/されている期間</t>
@@ -824,7 +839,16 @@
     <t>Practitioner.address.id</t>
   </si>
   <si>
+    <t>要素間参照のための一意のID / Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>リソース内の要素の一意のID（内部参照用）。これは、スペースを含まない文字列値である場合があります。 / Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
     <t>Practitioner.address.extension</t>
+  </si>
+  <si>
+    <t>要素の基本的な定義の一部ではない追加情報を表すために使用できます。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たされる一連の要件があります。 / May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
     <t>Practitioner.address.use</t>
@@ -845,13 +869,13 @@
 　- billing : 請求書、インボイス、領収書などの送付用</t>
   </si>
   <si>
-    <t>Allows an appropriate address to be chosen from a list of many.</t>
+    <t>多くのリストから適切なアドレスを選択できるようにします。 / Allows an appropriate address to be chosen from a list of many.</t>
   </si>
   <si>
     <t>home</t>
   </si>
   <si>
-    <t>The use of an address (home / work / etc.).</t>
+    <t>住所の用途（自宅 / 勤務先など）。 / The use of an address (home / work / etc.).</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/address-use|4.3.0</t>
@@ -884,7 +908,7 @@
     <t>both</t>
   </si>
   <si>
-    <t>The type of an address (physical / postal).</t>
+    <t>住所の種類（物理的 / 郵便）。 / The type of an address (physical / postal).</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/address-type|4.3.0</t>
@@ -913,7 +937,7 @@
 例：東京都文京区本郷7-3-1</t>
   </si>
   <si>
-    <t>A renderable, unencoded form.</t>
+    <t>レンダリング可能で、不コード化されていないフォーム。 / A renderable, unencoded form.</t>
   </si>
   <si>
     <t>137 Nowhere Street, Erewhon 9132</t>
@@ -1001,7 +1025,7 @@
     <t>地区名 【JP_Patient.address参照】</t>
   </si>
   <si>
-    <t>The name of the administrative area (county).</t>
+    <t>管理エリア（郡）の名前。 / The name of the administrative area (county).</t>
   </si>
   <si>
     <t>【JP Core仕様】日本の住所では使用しない。</t>
@@ -1057,7 +1081,7 @@
     <t>郵便番号 【JP_Patient.address参照】</t>
   </si>
   <si>
-    <t>A postal code designating a region defined by the postal service.</t>
+    <t>郵便サービスによって定義された地域を指定する郵便番号。 / A postal code designating a region defined by the postal service.</t>
   </si>
   <si>
     <t>郵便番号。日本の郵便番号の場合には3桁数字とハイフン1文字と4桁数字からなる半角８文字、または最初の3桁だけの3文字のいずれかとする。 例：113-8655</t>
@@ -1111,7 +1135,7 @@
     <t>住所が使用されていた/されている期間。 期間は時間の範囲を指定する。使用状況はその期間全体に適用されるか、範囲から1つの値が適用される。  期間は、時間間隔（経過時間の測定値）には使用されない。</t>
   </si>
   <si>
-    <t>Allows addresses to be placed in historical context.</t>
+    <t>アドレスを履歴上の文脈に配置できるようにします。 / Allows addresses to be placed in historical context.</t>
   </si>
   <si>
     <t>&lt;valuePeriod xmlns="http://hl7.org/fhir"&gt;
@@ -1129,7 +1153,7 @@
     <t>Practitioner.gender</t>
   </si>
   <si>
-    <t>male | female | other | unknown</t>
+    <t>男性|女性|その他|わからない / male | female | other | unknown</t>
   </si>
   <si>
     <t>管理や記録のためにその人が持っていると思われる性別。</t>
@@ -1138,7 +1162,7 @@
     <t>正しく相手に対応する必要がある。</t>
   </si>
   <si>
-    <t>The gender of a person used for administrative purposes.</t>
+    <t>管理目的で使用される人の性別。 / The gender of a person used for administrative purposes.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/administrative-gender|4.3.0</t>
@@ -1182,7 +1206,7 @@
 </t>
   </si>
   <si>
-    <t>Image of the person</t>
+    <t>人の画像 / Image of the person</t>
   </si>
   <si>
     <t>医療従事者の写真。</t>
@@ -1225,7 +1249,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
+    <t xml:space="preserve">ele-1:空のParametersリソースでない限り、すべてのFHIR要素には@valueまたはchildrenが必要です / All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
 </t>
   </si>
   <si>
@@ -1251,10 +1275,11 @@
 user contentmodifiers</t>
   </si>
   <si>
-    <t>Extensions that cannot be ignored even if unrecognized</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+    <t>認識されていなくても無視できない拡張機能 / Extensions that cannot be ignored even if unrecognized</t>
+  </si>
+  <si>
+    <t>要素の基本的な定義の一部ではなく、それが含まれている要素の理解、および/または含まれる要素の子孫の理解を変更するために使用される場合があります。通常、修飾子要素は否定または資格を提供します。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たされる一連の要件があります。アプリケーションの処理リソースは、修飾子拡張機能をチェックする必要があります。
+モディファイア拡張は、リソースまたはdomainResource上の要素の意味を変更してはなりません（修飾軸自体の意味を変更することはできません）。 / May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
@@ -1264,7 +1289,7 @@
     <t>Practitioner.qualification.identifier</t>
   </si>
   <si>
-    <t>An identifier for this qualification for the practitioner</t>
+    <t>開業医のこの資格のidentifier / An identifier for this qualification for the practitioner</t>
   </si>
   <si>
     <t>この人物のこの役割における資格に適用される識別子。</t>
@@ -1291,7 +1316,7 @@
 </t>
   </si>
   <si>
-    <t>Coded representation of the qualification</t>
+    <t>資格のコード化された表現 / Coded representation of the qualification</t>
   </si>
   <si>
     <t>資格のコード化された表現。</t>
@@ -1303,7 +1328,7 @@
     <t>example</t>
   </si>
   <si>
-    <t>Specific qualification the practitioner has to provide a service.</t>
+    <t>特定の資格開業医はサービスを提供する必要があります。 / Specific qualification the practitioner has to provide a service.</t>
   </si>
   <si>
     <t>http://terminology.hl7.org/ValueSet/v2-2.7-0360</t>
@@ -1315,7 +1340,7 @@
     <t>Practitioner.qualification.period</t>
   </si>
   <si>
-    <t>Period during which the qualification is valid</t>
+    <t>資格が有効な期間 / Period during which the qualification is valid</t>
   </si>
   <si>
     <t>資格が有効な期間。</t>
@@ -1341,7 +1366,7 @@
 </t>
   </si>
   <si>
-    <t>Organization that regulates and issues the qualification</t>
+    <t>資格を規制および発行する組織 / Organization that regulates and issues the qualification</t>
   </si>
   <si>
     <t>資格を規制し、発行する機関</t>
@@ -1362,10 +1387,10 @@
     <t>47</t>
   </si>
   <si>
-    <t>Certification, licenses, or training pertaining to the provision of care</t>
-  </si>
-  <si>
-    <t>The official certifications, training, and licenses that authorize or otherwise pertain to the provision of care by the practitioner.  For example, a medical license issued by a medical board authorizing the practitioner to practice medicine within a certian locality.</t>
+    <t>ケアの提供に関する認定、ライセンス、またはトレーニング / Certification, licenses, or training pertaining to the provision of care</t>
+  </si>
+  <si>
+    <t>開業医によるケアの提供に承認またはその他の方法である公式認定、トレーニング、およびライセンス。たとえば、医療委員会によって発行された医療免許は、実務家に証明書の地域内で医学を実践することを許可しています。 / The official certifications, training, and licenses that authorize or otherwise pertain to the provision of care by the practitioner.  For example, a medical license issued by a medical board authorizing the practitioner to practice medicine within a certian locality.</t>
   </si>
   <si>
     <t>Practitioner.qualification:narcoticPrescriptionLicenseNumber.id</t>
@@ -1401,16 +1426,16 @@
     <t>Practitioner.qualification.identifier.use</t>
   </si>
   <si>
-    <t>usual | official | temp | secondary | old (If known)</t>
-  </si>
-  <si>
-    <t>The purpose of this identifier.</t>
-  </si>
-  <si>
-    <t>Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
-  </si>
-  <si>
-    <t>Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
+    <t>通常|公式|一時的|セカンダリ|古い（知られている場合） / usual | official | temp | secondary | old (If known)</t>
+  </si>
+  <si>
+    <t>このidentifierの目的。 / The purpose of this identifier.</t>
+  </si>
+  <si>
+    <t>アプリケーションは、identifierが一時的なものであると明示的に言っていない限り、永続的であると想定できます。 / Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
+  </si>
+  <si>
+    <t>特定の使用のコンテキストが一連のidentifierの中から選択される適切なidentifierを許可します。 / Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/identifier-use|4.3.0</t>
@@ -1428,16 +1453,16 @@
     <t>Practitioner.qualification.identifier.type</t>
   </si>
   <si>
-    <t>Description of identifier</t>
-  </si>
-  <si>
-    <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
-  </si>
-  <si>
-    <t>Allows users to make use of identifiers when the identifier system is not known.</t>
+    <t>identifierの説明 / Description of identifier</t>
+  </si>
+  <si>
+    <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>この要素は、identifierの一般的なカテゴリのみを扱います。identifier。システムに対応するコードに使用しないでください。一部のidentifierは、一般的な使用法により複数のカテゴリに分類される場合があります。システムがわかっている場合、タイプは常にシステム定義の一部であるため、タイプは不要です。ただし、システムが不明なidentifierを処理する必要があることがよくあります。多くの異なるシステムが同じタイプを持っているため、タイプとシステムの間に1：1の関係はありません。 / This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
+  </si>
+  <si>
+    <t>identifierシステムが不明な場合、ユーザーはidentifierを使用できます。 / Allows users to make use of identifiers when the identifier system is not known.</t>
   </si>
   <si>
     <t>extensible</t>
@@ -1515,7 +1540,7 @@
 　- urn:oid:1.2.392.100495.20.3.32.147(沖縄県)</t>
   </si>
   <si>
-    <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
+    <t>identifierのセットがたくさんあります。2つのidentifierを一致させるには、どのセットを扱っているかを知る必要があります。システムは、特定の一意のidentifierセットを識別します。 / There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
     <t>http://www.acme.com/identifiers/patient</t>
@@ -1542,7 +1567,7 @@
     <t>都道府県別　麻薬施用者免許番号 【詳細参照】</t>
   </si>
   <si>
-    <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
+    <t>通常、identifierの部分はユーザーに関連し、システムのコンテキスト内で一意のユーザーに関連しています。 / The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
   </si>
   <si>
     <t>都道府県別　麻薬施用者免許番号</t>
@@ -1566,10 +1591,10 @@
     <t>Practitioner.qualification.identifier.period</t>
   </si>
   <si>
-    <t>Time period when id is/was valid for use</t>
-  </si>
-  <si>
-    <t>Time period during which identifier is/was valid for use.</t>
+    <t>IDが使用に有効だった時間期間 / Time period when id is/was valid for use</t>
+  </si>
+  <si>
+    <t>identifierが使用される/有効な期間。 / Time period during which identifier is/was valid for use.</t>
   </si>
   <si>
     <t>Identifier.period</t>
@@ -1591,13 +1616,13 @@
 </t>
   </si>
   <si>
-    <t>Organization that issued id (may be just text)</t>
-  </si>
-  <si>
-    <t>Organization that issued/manages the identifier.</t>
-  </si>
-  <si>
-    <t>The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
+    <t>IDを発行した組織（単なるテキストである可能性があります） / Organization that issued id (may be just text)</t>
+  </si>
+  <si>
+    <t>identifierを発行/管理する組織。 / Organization that issued/manages the identifier.</t>
+  </si>
+  <si>
+    <t>identifierは、.reference要素を省略し、割り当て組織に関する名前またはその他のテキスト情報を反映した.display要素のみを含む場合があります。 / The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
   </si>
   <si>
     <t>Identifier.assigner</t>
@@ -1668,13 +1693,13 @@
     <t>Practitioner.qualification:medicalRegistrationNumber.identifier.system</t>
   </si>
   <si>
-    <t>The namespace for the identifier value</t>
-  </si>
-  <si>
-    <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
-  </si>
-  <si>
-    <t>Identifier.system is always case sensitive.</t>
+    <t>identifier値の名前空間 / The namespace for the identifier value</t>
+  </si>
+  <si>
+    <t>値の名前空間、つまり一意のセット値を記述するURLを確立します。 / Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
+  </si>
+  <si>
+    <t>identifier。システムは常にケースに敏感です。 / Identifier.system is always case sensitive.</t>
   </si>
   <si>
     <t>http://jpfhir.jp/fhir/core/mhlw/IdSystem/medicalRegistrationNumber</t>
@@ -2058,7 +2083,7 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="49.78125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="75.83203125" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="52.0859375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
@@ -3830,13 +3855,13 @@
         <v>137</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>138</v>
+        <v>191</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>140</v>
+        <v>193</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3874,19 +3899,19 @@
         <v>78</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="AD16" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
@@ -3898,7 +3923,7 @@
         <v>78</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>142</v>
+        <v>198</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>78</v>
@@ -3915,10 +3940,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3944,13 +3969,13 @@
         <v>110</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3976,11 +4001,11 @@
         <v>78</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="Y17" s="2"/>
       <c r="Z17" t="s" s="2">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>78</v>
@@ -3998,7 +4023,7 @@
         <v>78</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -4007,19 +4032,19 @@
         <v>90</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>102</v>
+        <v>207</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>78</v>
@@ -4027,10 +4052,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4053,19 +4078,19 @@
         <v>91</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>78</v>
@@ -4114,7 +4139,7 @@
         <v>78</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
@@ -4126,16 +4151,16 @@
         <v>78</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>102</v>
+        <v>207</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>78</v>
@@ -4143,10 +4168,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4172,16 +4197,16 @@
         <v>110</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>78</v>
@@ -4206,11 +4231,11 @@
         <v>78</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="Y19" s="2"/>
       <c r="Z19" t="s" s="2">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>78</v>
@@ -4228,7 +4253,7 @@
         <v>78</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
@@ -4240,16 +4265,16 @@
         <v>78</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>102</v>
+        <v>207</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>78</v>
@@ -4257,10 +4282,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4283,16 +4308,16 @@
         <v>91</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4342,7 +4367,7 @@
         <v>78</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -4354,7 +4379,7 @@
         <v>78</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>102</v>
+        <v>207</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>189</v>
@@ -4371,10 +4396,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4397,16 +4422,16 @@
         <v>91</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4456,7 +4481,7 @@
         <v>78</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -4468,16 +4493,16 @@
         <v>78</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>102</v>
+        <v>207</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>134</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>78</v>
@@ -4485,10 +4510,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4511,19 +4536,19 @@
         <v>91</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>78</v>
@@ -4572,7 +4597,7 @@
         <v>78</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -4587,13 +4612,13 @@
         <v>102</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>78</v>
@@ -4601,10 +4626,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4630,10 +4655,10 @@
         <v>92</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>186</v>
+        <v>255</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>187</v>
+        <v>256</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4713,10 +4738,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4745,7 +4770,7 @@
         <v>138</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>191</v>
+        <v>258</v>
       </c>
       <c r="N24" t="s" s="2">
         <v>140</v>
@@ -4786,19 +4811,19 @@
         <v>78</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -4827,10 +4852,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4856,16 +4881,16 @@
         <v>110</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>78</v>
@@ -4878,7 +4903,7 @@
         <v>78</v>
       </c>
       <c r="T25" t="s" s="2">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="U25" t="s" s="2">
         <v>78</v>
@@ -4890,13 +4915,13 @@
         <v>78</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>78</v>
@@ -4914,7 +4939,7 @@
         <v>78</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -4929,13 +4954,13 @@
         <v>102</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>78</v>
@@ -4943,10 +4968,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4972,13 +4997,13 @@
         <v>110</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4992,7 +5017,7 @@
         <v>78</v>
       </c>
       <c r="T26" t="s" s="2">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="U26" t="s" s="2">
         <v>78</v>
@@ -5004,13 +5029,13 @@
         <v>78</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>78</v>
@@ -5028,7 +5053,7 @@
         <v>78</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -5043,10 +5068,10 @@
         <v>102</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>78</v>
@@ -5057,10 +5082,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5083,19 +5108,19 @@
         <v>91</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>78</v>
@@ -5108,7 +5133,7 @@
         <v>78</v>
       </c>
       <c r="T27" t="s" s="2">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="U27" t="s" s="2">
         <v>78</v>
@@ -5144,7 +5169,7 @@
         <v>78</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -5159,10 +5184,10 @@
         <v>102</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>78</v>
@@ -5173,10 +5198,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5199,16 +5224,16 @@
         <v>91</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5222,7 +5247,7 @@
         <v>78</v>
       </c>
       <c r="T28" t="s" s="2">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="U28" t="s" s="2">
         <v>78</v>
@@ -5258,7 +5283,7 @@
         <v>78</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -5273,13 +5298,13 @@
         <v>102</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>78</v>
@@ -5287,14 +5312,14 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -5313,16 +5338,16 @@
         <v>91</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5336,7 +5361,7 @@
         <v>78</v>
       </c>
       <c r="T29" t="s" s="2">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="U29" t="s" s="2">
         <v>78</v>
@@ -5372,7 +5397,7 @@
         <v>78</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -5387,13 +5412,13 @@
         <v>102</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>78</v>
@@ -5401,14 +5426,14 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -5427,16 +5452,16 @@
         <v>91</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5450,7 +5475,7 @@
         <v>78</v>
       </c>
       <c r="T30" t="s" s="2">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="U30" t="s" s="2">
         <v>78</v>
@@ -5486,7 +5511,7 @@
         <v>78</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -5501,10 +5526,10 @@
         <v>102</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>78</v>
@@ -5515,14 +5540,14 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -5541,16 +5566,16 @@
         <v>91</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5600,7 +5625,7 @@
         <v>78</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5615,13 +5640,13 @@
         <v>102</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>78</v>
@@ -5629,14 +5654,14 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5655,16 +5680,16 @@
         <v>91</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5678,7 +5703,7 @@
         <v>78</v>
       </c>
       <c r="T32" t="s" s="2">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="U32" t="s" s="2">
         <v>78</v>
@@ -5714,7 +5739,7 @@
         <v>78</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -5729,13 +5754,13 @@
         <v>102</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>78</v>
@@ -5743,10 +5768,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5769,16 +5794,16 @@
         <v>91</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5828,7 +5853,7 @@
         <v>78</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -5843,13 +5868,13 @@
         <v>102</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>78</v>
@@ -5857,10 +5882,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5883,19 +5908,19 @@
         <v>91</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>78</v>
@@ -5908,7 +5933,7 @@
         <v>78</v>
       </c>
       <c r="T34" t="s" s="2">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="U34" t="s" s="2">
         <v>78</v>
@@ -5944,7 +5969,7 @@
         <v>78</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -5959,13 +5984,13 @@
         <v>102</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>78</v>
@@ -5973,10 +5998,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6002,14 +6027,14 @@
         <v>110</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>78</v>
@@ -6034,13 +6059,13 @@
         <v>78</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>78</v>
@@ -6058,7 +6083,7 @@
         <v>78</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -6073,13 +6098,13 @@
         <v>102</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>78</v>
@@ -6087,10 +6112,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6113,17 +6138,17 @@
         <v>91</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>78</v>
@@ -6172,7 +6197,7 @@
         <v>78</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -6187,13 +6212,13 @@
         <v>102</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>78</v>
@@ -6201,10 +6226,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6227,19 +6252,19 @@
         <v>78</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>78</v>
@@ -6288,7 +6313,7 @@
         <v>78</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -6306,10 +6331,10 @@
         <v>78</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>78</v>
@@ -6317,10 +6342,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6343,16 +6368,16 @@
         <v>78</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6390,17 +6415,17 @@
         <v>78</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="AC38" s="2"/>
       <c r="AD38" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -6412,16 +6437,16 @@
         <v>78</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>375</v>
+        <v>382</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>78</v>
@@ -6429,10 +6454,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6455,13 +6480,13 @@
         <v>78</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>186</v>
+        <v>255</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>187</v>
+        <v>256</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6541,10 +6566,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6573,7 +6598,7 @@
         <v>138</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>191</v>
+        <v>258</v>
       </c>
       <c r="N40" t="s" s="2">
         <v>140</v>
@@ -6626,7 +6651,7 @@
         <v>78</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -6655,14 +6680,14 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -6684,10 +6709,10 @@
         <v>137</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="N41" t="s" s="2">
         <v>140</v>
@@ -6742,7 +6767,7 @@
         <v>78</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>383</v>
+        <v>390</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -6771,10 +6796,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6800,16 +6825,16 @@
         <v>149</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>388</v>
+        <v>395</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>78</v>
@@ -6858,7 +6883,7 @@
         <v>78</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -6876,7 +6901,7 @@
         <v>78</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>78</v>
@@ -6887,10 +6912,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6913,16 +6938,16 @@
         <v>78</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>393</v>
+        <v>400</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>394</v>
+        <v>401</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6948,31 +6973,31 @@
         <v>78</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>395</v>
+        <v>402</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>396</v>
+        <v>403</v>
       </c>
       <c r="Z43" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="AA43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF43" t="s" s="2">
         <v>397</v>
-      </c>
-      <c r="AA43" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB43" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC43" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD43" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE43" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF43" t="s" s="2">
-        <v>390</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>90</v>
@@ -6990,10 +7015,10 @@
         <v>78</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>375</v>
+        <v>382</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>78</v>
@@ -7001,10 +7026,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7027,19 +7052,19 @@
         <v>78</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>78</v>
@@ -7088,7 +7113,7 @@
         <v>78</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -7106,10 +7131,10 @@
         <v>78</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>404</v>
+        <v>411</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>405</v>
+        <v>412</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>78</v>
@@ -7117,10 +7142,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7143,16 +7168,16 @@
         <v>78</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>410</v>
+        <v>417</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7202,7 +7227,7 @@
         <v>78</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -7220,7 +7245,7 @@
         <v>78</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>78</v>
@@ -7231,13 +7256,13 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>412</v>
+        <v>419</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="D46" t="s" s="2">
         <v>78</v>
@@ -7247,7 +7272,7 @@
         <v>79</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>78</v>
@@ -7259,13 +7284,13 @@
         <v>78</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7316,7 +7341,7 @@
         <v>78</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -7328,16 +7353,16 @@
         <v>78</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>375</v>
+        <v>382</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>78</v>
@@ -7345,10 +7370,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7371,13 +7396,13 @@
         <v>78</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>186</v>
+        <v>255</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>187</v>
+        <v>256</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7457,10 +7482,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7489,7 +7514,7 @@
         <v>138</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>191</v>
+        <v>258</v>
       </c>
       <c r="N48" t="s" s="2">
         <v>140</v>
@@ -7542,7 +7567,7 @@
         <v>78</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7571,14 +7596,14 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7600,10 +7625,10 @@
         <v>137</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="N49" t="s" s="2">
         <v>140</v>
@@ -7658,7 +7683,7 @@
         <v>78</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>383</v>
+        <v>390</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -7687,10 +7712,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7716,16 +7741,16 @@
         <v>149</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>388</v>
+        <v>395</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>78</v>
@@ -7774,7 +7799,7 @@
         <v>78</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -7792,7 +7817,7 @@
         <v>78</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>78</v>
@@ -7803,10 +7828,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7832,10 +7857,10 @@
         <v>92</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>186</v>
+        <v>255</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>187</v>
+        <v>256</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7915,10 +7940,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7947,7 +7972,7 @@
         <v>138</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>191</v>
+        <v>258</v>
       </c>
       <c r="N52" t="s" s="2">
         <v>140</v>
@@ -7988,19 +8013,19 @@
         <v>78</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="AC52" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="AD52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -8029,10 +8054,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>427</v>
+        <v>434</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8058,16 +8083,16 @@
         <v>110</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>428</v>
+        <v>435</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>429</v>
+        <v>436</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>430</v>
+        <v>437</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>431</v>
+        <v>438</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>78</v>
@@ -8092,11 +8117,11 @@
         <v>78</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="Y53" s="2"/>
       <c r="Z53" t="s" s="2">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>78</v>
@@ -8114,7 +8139,7 @@
         <v>78</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>433</v>
+        <v>440</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -8132,7 +8157,7 @@
         <v>134</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>78</v>
@@ -8143,10 +8168,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>436</v>
+        <v>443</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8169,19 +8194,19 @@
         <v>91</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>437</v>
+        <v>444</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>439</v>
+        <v>446</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>440</v>
+        <v>447</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>78</v>
@@ -8206,11 +8231,11 @@
         <v>78</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>441</v>
+        <v>448</v>
       </c>
       <c r="Y54" s="2"/>
       <c r="Z54" t="s" s="2">
-        <v>442</v>
+        <v>449</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>78</v>
@@ -8228,7 +8253,7 @@
         <v>78</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>443</v>
+        <v>450</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8243,10 +8268,10 @@
         <v>102</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>444</v>
+        <v>451</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>78</v>
@@ -8257,10 +8282,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>445</v>
+        <v>452</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>446</v>
+        <v>453</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8286,16 +8311,16 @@
         <v>104</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>449</v>
+        <v>456</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>450</v>
+        <v>457</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>78</v>
@@ -8308,7 +8333,7 @@
         <v>78</v>
       </c>
       <c r="T55" t="s" s="2">
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="U55" t="s" s="2">
         <v>78</v>
@@ -8344,7 +8369,7 @@
         <v>78</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>452</v>
+        <v>459</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8359,13 +8384,13 @@
         <v>102</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>453</v>
+        <v>460</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>454</v>
+        <v>461</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>455</v>
+        <v>462</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>78</v>
@@ -8373,10 +8398,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>456</v>
+        <v>463</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>457</v>
+        <v>464</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8399,16 +8424,16 @@
         <v>91</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>458</v>
+        <v>465</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>459</v>
+        <v>466</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>460</v>
+        <v>467</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8422,7 +8447,7 @@
         <v>78</v>
       </c>
       <c r="T56" t="s" s="2">
-        <v>461</v>
+        <v>468</v>
       </c>
       <c r="U56" t="s" s="2">
         <v>78</v>
@@ -8458,7 +8483,7 @@
         <v>78</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>462</v>
+        <v>469</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8473,13 +8498,13 @@
         <v>102</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>463</v>
+        <v>470</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>78</v>
@@ -8487,10 +8512,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>465</v>
+        <v>472</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>466</v>
+        <v>473</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8513,13 +8538,13 @@
         <v>91</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>467</v>
+        <v>474</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>468</v>
+        <v>475</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8570,7 +8595,7 @@
         <v>78</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>469</v>
+        <v>476</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -8585,13 +8610,13 @@
         <v>102</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>470</v>
+        <v>477</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>471</v>
+        <v>478</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>78</v>
@@ -8599,10 +8624,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>472</v>
+        <v>479</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>473</v>
+        <v>480</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8625,16 +8650,16 @@
         <v>91</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>474</v>
+        <v>481</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>475</v>
+        <v>482</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>476</v>
+        <v>483</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>477</v>
+        <v>484</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8684,7 +8709,7 @@
         <v>78</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>478</v>
+        <v>485</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8699,13 +8724,13 @@
         <v>102</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>479</v>
+        <v>486</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>480</v>
+        <v>487</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>481</v>
+        <v>488</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>78</v>
@@ -8713,10 +8738,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>482</v>
+        <v>489</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8739,16 +8764,16 @@
         <v>78</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>393</v>
+        <v>400</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>394</v>
+        <v>401</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -8759,7 +8784,7 @@
         <v>78</v>
       </c>
       <c r="S59" t="s" s="2">
-        <v>483</v>
+        <v>490</v>
       </c>
       <c r="T59" t="s" s="2">
         <v>78</v>
@@ -8774,11 +8799,11 @@
         <v>78</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="Y59" s="2"/>
       <c r="Z59" t="s" s="2">
-        <v>484</v>
+        <v>491</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>78</v>
@@ -8796,7 +8821,7 @@
         <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>90</v>
@@ -8814,10 +8839,10 @@
         <v>78</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>375</v>
+        <v>382</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>78</v>
@@ -8825,10 +8850,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>485</v>
+        <v>492</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8851,19 +8876,19 @@
         <v>78</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>78</v>
@@ -8912,7 +8937,7 @@
         <v>78</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -8930,10 +8955,10 @@
         <v>78</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>404</v>
+        <v>411</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>405</v>
+        <v>412</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>78</v>
@@ -8941,10 +8966,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8967,16 +8992,16 @@
         <v>78</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>474</v>
+        <v>481</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>410</v>
+        <v>417</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9026,7 +9051,7 @@
         <v>78</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -9044,7 +9069,7 @@
         <v>78</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>78</v>
@@ -9055,13 +9080,13 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>487</v>
+        <v>494</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="C62" t="s" s="2">
-        <v>488</v>
+        <v>495</v>
       </c>
       <c r="D62" t="s" s="2">
         <v>78</v>
@@ -9083,13 +9108,13 @@
         <v>78</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9140,7 +9165,7 @@
         <v>78</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -9152,16 +9177,16 @@
         <v>78</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>375</v>
+        <v>382</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>78</v>
@@ -9169,10 +9194,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>489</v>
+        <v>496</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9195,13 +9220,13 @@
         <v>78</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>186</v>
+        <v>255</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>187</v>
+        <v>256</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9281,10 +9306,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>490</v>
+        <v>497</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9313,7 +9338,7 @@
         <v>138</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>191</v>
+        <v>258</v>
       </c>
       <c r="N64" t="s" s="2">
         <v>140</v>
@@ -9366,7 +9391,7 @@
         <v>78</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -9395,14 +9420,14 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>491</v>
+        <v>498</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -9424,10 +9449,10 @@
         <v>137</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="N65" t="s" s="2">
         <v>140</v>
@@ -9482,7 +9507,7 @@
         <v>78</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>383</v>
+        <v>390</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -9511,10 +9536,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>492</v>
+        <v>499</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9540,16 +9565,16 @@
         <v>149</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>493</v>
+        <v>500</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>388</v>
+        <v>395</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>78</v>
@@ -9598,7 +9623,7 @@
         <v>78</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -9616,7 +9641,7 @@
         <v>78</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>78</v>
@@ -9627,10 +9652,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>494</v>
+        <v>501</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9656,10 +9681,10 @@
         <v>92</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>186</v>
+        <v>255</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>187</v>
+        <v>256</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9739,10 +9764,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>495</v>
+        <v>502</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9771,7 +9796,7 @@
         <v>138</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>191</v>
+        <v>258</v>
       </c>
       <c r="N68" t="s" s="2">
         <v>140</v>
@@ -9812,19 +9837,19 @@
         <v>78</v>
       </c>
       <c r="AB68" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="AC68" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="AD68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE68" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -9853,10 +9878,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>496</v>
+        <v>503</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>427</v>
+        <v>434</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9882,16 +9907,16 @@
         <v>110</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>428</v>
+        <v>435</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>429</v>
+        <v>436</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>430</v>
+        <v>437</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>431</v>
+        <v>438</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>78</v>
@@ -9916,11 +9941,11 @@
         <v>78</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="Y69" s="2"/>
       <c r="Z69" t="s" s="2">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>78</v>
@@ -9938,7 +9963,7 @@
         <v>78</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>433</v>
+        <v>440</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -9956,7 +9981,7 @@
         <v>134</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>78</v>
@@ -9967,10 +9992,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>497</v>
+        <v>504</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>436</v>
+        <v>443</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9993,19 +10018,19 @@
         <v>91</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>437</v>
+        <v>444</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>439</v>
+        <v>446</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>440</v>
+        <v>447</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>78</v>
@@ -10030,11 +10055,11 @@
         <v>78</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>441</v>
+        <v>448</v>
       </c>
       <c r="Y70" s="2"/>
       <c r="Z70" t="s" s="2">
-        <v>442</v>
+        <v>449</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>78</v>
@@ -10052,7 +10077,7 @@
         <v>78</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>443</v>
+        <v>450</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -10067,10 +10092,10 @@
         <v>102</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>444</v>
+        <v>451</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>78</v>
@@ -10081,10 +10106,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>498</v>
+        <v>505</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>446</v>
+        <v>453</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10110,29 +10135,29 @@
         <v>104</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>499</v>
+        <v>506</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>500</v>
+        <v>507</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>501</v>
+        <v>508</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>450</v>
+        <v>457</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q71" s="2"/>
       <c r="R71" t="s" s="2">
-        <v>502</v>
+        <v>509</v>
       </c>
       <c r="S71" t="s" s="2">
         <v>78</v>
       </c>
       <c r="T71" t="s" s="2">
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="U71" t="s" s="2">
         <v>78</v>
@@ -10168,7 +10193,7 @@
         <v>78</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>452</v>
+        <v>459</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -10183,13 +10208,13 @@
         <v>102</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>453</v>
+        <v>460</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>454</v>
+        <v>461</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>455</v>
+        <v>462</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>78</v>
@@ -10197,10 +10222,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>503</v>
+        <v>510</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>457</v>
+        <v>464</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10223,16 +10248,16 @@
         <v>91</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>493</v>
+        <v>500</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>459</v>
+        <v>466</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>493</v>
+        <v>500</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10246,7 +10271,7 @@
         <v>78</v>
       </c>
       <c r="T72" t="s" s="2">
-        <v>461</v>
+        <v>468</v>
       </c>
       <c r="U72" t="s" s="2">
         <v>78</v>
@@ -10282,7 +10307,7 @@
         <v>78</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>462</v>
+        <v>469</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10297,13 +10322,13 @@
         <v>102</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>463</v>
+        <v>470</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>78</v>
@@ -10311,10 +10336,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>504</v>
+        <v>511</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>466</v>
+        <v>473</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10337,13 +10362,13 @@
         <v>91</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>467</v>
+        <v>474</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>468</v>
+        <v>475</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10394,7 +10419,7 @@
         <v>78</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>469</v>
+        <v>476</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -10409,13 +10434,13 @@
         <v>102</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>470</v>
+        <v>477</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>471</v>
+        <v>478</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>78</v>
@@ -10423,10 +10448,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>505</v>
+        <v>512</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>473</v>
+        <v>480</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10449,16 +10474,16 @@
         <v>91</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>474</v>
+        <v>481</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>475</v>
+        <v>482</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>476</v>
+        <v>483</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>477</v>
+        <v>484</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -10508,7 +10533,7 @@
         <v>78</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>478</v>
+        <v>485</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -10523,13 +10548,13 @@
         <v>102</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>479</v>
+        <v>486</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>480</v>
+        <v>487</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>481</v>
+        <v>488</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>78</v>
@@ -10537,10 +10562,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>506</v>
+        <v>513</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10563,16 +10588,16 @@
         <v>78</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>393</v>
+        <v>400</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>394</v>
+        <v>401</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -10583,7 +10608,7 @@
         <v>78</v>
       </c>
       <c r="S75" t="s" s="2">
-        <v>507</v>
+        <v>514</v>
       </c>
       <c r="T75" t="s" s="2">
         <v>78</v>
@@ -10598,11 +10623,11 @@
         <v>78</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="Y75" s="2"/>
       <c r="Z75" t="s" s="2">
-        <v>484</v>
+        <v>491</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>78</v>
@@ -10620,7 +10645,7 @@
         <v>78</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>90</v>
@@ -10638,10 +10663,10 @@
         <v>78</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>375</v>
+        <v>382</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>78</v>
@@ -10649,10 +10674,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>508</v>
+        <v>515</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10675,19 +10700,19 @@
         <v>78</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>78</v>
@@ -10736,7 +10761,7 @@
         <v>78</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
@@ -10754,10 +10779,10 @@
         <v>78</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>404</v>
+        <v>411</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>405</v>
+        <v>412</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>78</v>
@@ -10765,10 +10790,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>509</v>
+        <v>516</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10791,16 +10816,16 @@
         <v>78</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>474</v>
+        <v>481</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>410</v>
+        <v>417</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -10850,7 +10875,7 @@
         <v>78</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
@@ -10868,7 +10893,7 @@
         <v>78</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>78</v>
@@ -10879,10 +10904,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>510</v>
+        <v>517</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>510</v>
+        <v>517</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10905,19 +10930,19 @@
         <v>78</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>511</v>
+        <v>518</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>512</v>
+        <v>519</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>513</v>
+        <v>520</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>78</v>
@@ -10966,7 +10991,7 @@
         <v>78</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>510</v>
+        <v>517</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
@@ -10981,13 +11006,13 @@
         <v>102</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>516</v>
+        <v>523</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>517</v>
+        <v>524</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>78</v>
